--- a/artfynd/A 25016-2025 artfynd.xlsx
+++ b/artfynd/A 25016-2025 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127103766</v>
+        <v>127103710</v>
       </c>
       <c r="B12" t="n">
-        <v>57654</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,39 +1806,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Häbbersjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596522</v>
+        <v>596551</v>
       </c>
       <c r="R12" t="n">
-        <v>6984832</v>
+        <v>6984851</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127103710</v>
+        <v>127103766</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,34 +1903,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Häbbersjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596551</v>
+        <v>596522</v>
       </c>
       <c r="R13" t="n">
-        <v>6984851</v>
+        <v>6984832</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2104,7 +2104,7 @@
         <v>127104594</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25016-2025 artfynd.xlsx
+++ b/artfynd/A 25016-2025 artfynd.xlsx
@@ -1798,7 +1798,7 @@
         <v>127103710</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>127104594</v>
       </c>
       <c r="B15" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25016-2025 artfynd.xlsx
+++ b/artfynd/A 25016-2025 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127103710</v>
+        <v>127103766</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,34 +1806,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Häbbersjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596551</v>
+        <v>596522</v>
       </c>
       <c r="R12" t="n">
-        <v>6984851</v>
+        <v>6984832</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,10 +1897,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127103766</v>
+        <v>127103710</v>
       </c>
       <c r="B13" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,39 +1908,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Häbbersjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596522</v>
+        <v>596551</v>
       </c>
       <c r="R13" t="n">
-        <v>6984832</v>
+        <v>6984851</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 25016-2025 artfynd.xlsx
+++ b/artfynd/A 25016-2025 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127103766</v>
+        <v>127103710</v>
       </c>
       <c r="B12" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,39 +1806,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Häbbersjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596522</v>
+        <v>596551</v>
       </c>
       <c r="R12" t="n">
-        <v>6984832</v>
+        <v>6984851</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127103710</v>
+        <v>127103766</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,34 +1903,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Häbbersjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596551</v>
+        <v>596522</v>
       </c>
       <c r="R13" t="n">
-        <v>6984851</v>
+        <v>6984832</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 25016-2025 artfynd.xlsx
+++ b/artfynd/A 25016-2025 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127103766</v>
+        <v>127103710</v>
       </c>
       <c r="B12" t="n">
-        <v>57654</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,39 +1806,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Häbbersjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596522</v>
+        <v>596551</v>
       </c>
       <c r="R12" t="n">
-        <v>6984832</v>
+        <v>6984851</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127103710</v>
+        <v>127103766</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,34 +1903,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Häbbersjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596551</v>
+        <v>596522</v>
       </c>
       <c r="R13" t="n">
-        <v>6984851</v>
+        <v>6984832</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1997,7 @@
         <v>127104113</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>127104594</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>127104070</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>127104643</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 25016-2025 artfynd.xlsx
+++ b/artfynd/A 25016-2025 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127103710</v>
+        <v>127103766</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,34 +1806,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Häbbersjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596551</v>
+        <v>596522</v>
       </c>
       <c r="R12" t="n">
-        <v>6984851</v>
+        <v>6984832</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,10 +1897,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127103766</v>
+        <v>127103710</v>
       </c>
       <c r="B13" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,39 +1908,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Häbbersjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596522</v>
+        <v>596551</v>
       </c>
       <c r="R13" t="n">
-        <v>6984832</v>
+        <v>6984851</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 25016-2025 artfynd.xlsx
+++ b/artfynd/A 25016-2025 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127103766</v>
+        <v>127103710</v>
       </c>
       <c r="B12" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,39 +1806,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Häbbersjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596522</v>
+        <v>596551</v>
       </c>
       <c r="R12" t="n">
-        <v>6984832</v>
+        <v>6984851</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127103710</v>
+        <v>127103766</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,34 +1903,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Häbbersjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596551</v>
+        <v>596522</v>
       </c>
       <c r="R13" t="n">
-        <v>6984851</v>
+        <v>6984832</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 25016-2025 artfynd.xlsx
+++ b/artfynd/A 25016-2025 artfynd.xlsx
@@ -1798,7 +1798,7 @@
         <v>127103710</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>127103766</v>
       </c>
       <c r="B13" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>127104113</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>127104594</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>127104070</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>127104643</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 25016-2025 artfynd.xlsx
+++ b/artfynd/A 25016-2025 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127103710</v>
+        <v>127103766</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,34 +1806,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Häbbersjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596551</v>
+        <v>596522</v>
       </c>
       <c r="R12" t="n">
-        <v>6984851</v>
+        <v>6984832</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,10 +1897,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127103766</v>
+        <v>127103710</v>
       </c>
       <c r="B13" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,39 +1908,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Häbbersjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596522</v>
+        <v>596551</v>
       </c>
       <c r="R13" t="n">
-        <v>6984832</v>
+        <v>6984851</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 25016-2025 artfynd.xlsx
+++ b/artfynd/A 25016-2025 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127103766</v>
+        <v>127103710</v>
       </c>
       <c r="B12" t="n">
-        <v>57660</v>
+        <v>79023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,39 +1806,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Häbbersjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596522</v>
+        <v>596551</v>
       </c>
       <c r="R12" t="n">
-        <v>6984832</v>
+        <v>6984851</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127103710</v>
+        <v>127103766</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,34 +1903,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Häbbersjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596551</v>
+        <v>596522</v>
       </c>
       <c r="R13" t="n">
-        <v>6984851</v>
+        <v>6984832</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1997,7 @@
         <v>127104113</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>127104594</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>127104070</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>127104643</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 25016-2025 artfynd.xlsx
+++ b/artfynd/A 25016-2025 artfynd.xlsx
@@ -1798,7 +1798,7 @@
         <v>127103710</v>
       </c>
       <c r="B12" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>127103766</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>127104113</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>127104594</v>
       </c>
       <c r="B15" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>127104070</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>127104643</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 25016-2025 artfynd.xlsx
+++ b/artfynd/A 25016-2025 artfynd.xlsx
@@ -1798,7 +1798,7 @@
         <v>127103710</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>127103766</v>
       </c>
       <c r="B13" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>127104113</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>127104594</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>127104070</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>127104643</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 25016-2025 artfynd.xlsx
+++ b/artfynd/A 25016-2025 artfynd.xlsx
@@ -1798,7 +1798,7 @@
         <v>127103710</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>127103766</v>
       </c>
       <c r="B13" t="n">
-        <v>57654</v>
+        <v>57669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>127104113</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>127104594</v>
       </c>
       <c r="B15" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>127104070</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>127104643</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 25016-2025 artfynd.xlsx
+++ b/artfynd/A 25016-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111350828</v>
+        <v>111350823</v>
       </c>
       <c r="B2" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596682.8394464939</v>
+        <v>597130</v>
       </c>
       <c r="R2" t="n">
-        <v>6984783.734535044</v>
+        <v>6984750</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111350830</v>
+        <v>111350827</v>
       </c>
       <c r="B3" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596682.8394464939</v>
+        <v>596697</v>
       </c>
       <c r="R3" t="n">
-        <v>6984783.734535044</v>
+        <v>6984740</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2023-08-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,19 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111350831</v>
+        <v>111350822</v>
       </c>
       <c r="B4" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596798.3808304428</v>
+        <v>597158</v>
       </c>
       <c r="R4" t="n">
-        <v>6984820.376245612</v>
+        <v>6984704</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111350827</v>
+        <v>111350824</v>
       </c>
       <c r="B5" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596696.4378522013</v>
+        <v>596877</v>
       </c>
       <c r="R5" t="n">
-        <v>6984740.007379165</v>
+        <v>6984615</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111350829</v>
+        <v>111350828</v>
       </c>
       <c r="B6" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596682.8394464939</v>
+        <v>596683</v>
       </c>
       <c r="R6" t="n">
-        <v>6984783.734535044</v>
+        <v>6984784</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2023-08-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111350823</v>
+        <v>111350831</v>
       </c>
       <c r="B7" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597129.3910494223</v>
+        <v>596799</v>
       </c>
       <c r="R7" t="n">
-        <v>6984750.609278883</v>
+        <v>6984820</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,22 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,50 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111350825</v>
+        <v>127103710</v>
       </c>
       <c r="B8" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Risåsen, Jmt</t>
+          <t>Häbbersjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596729.6433546353</v>
+        <v>596551</v>
       </c>
       <c r="R8" t="n">
-        <v>6984726.434217013</v>
+        <v>6984851</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,22 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,31 +1342,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111350824</v>
+        <v>127104594</v>
       </c>
       <c r="B9" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1495,14 +1385,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Risåsen, Jmt</t>
+          <t>Häbbersjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596876.9436261626</v>
+        <v>596846</v>
       </c>
       <c r="R9" t="n">
-        <v>6984614.337989948</v>
+        <v>6984733</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,22 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,49 +1439,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111350826</v>
+        <v>111350830</v>
       </c>
       <c r="B10" t="n">
-        <v>78611</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596729.6433546353</v>
+        <v>596683</v>
       </c>
       <c r="R10" t="n">
-        <v>6984726.434217013</v>
+        <v>6984784</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1519,9 @@
           <t>2023-08-03</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111350822</v>
+        <v>111350829</v>
       </c>
       <c r="B11" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597158.1255112892</v>
+        <v>596683</v>
       </c>
       <c r="R11" t="n">
-        <v>6984703.69465562</v>
+        <v>6984784</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,22 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,27 +1645,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127103710</v>
+        <v>111350826</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>80467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1826,14 +1676,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Häbbersjöhöjden, Jmt</t>
+          <t>Risåsen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596551</v>
+        <v>596730</v>
       </c>
       <c r="R12" t="n">
-        <v>6984851</v>
+        <v>6984727</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,12 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,12 +1730,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1895,11 +1745,11 @@
         <v>127103766</v>
       </c>
       <c r="B13" t="n">
-        <v>57669</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1994,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127104113</v>
+        <v>127104070</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2034,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596612</v>
+        <v>596613</v>
       </c>
       <c r="R14" t="n">
-        <v>6984853</v>
+        <v>6984838</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2101,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127104594</v>
+        <v>127104113</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2112,34 +1962,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Häbbersjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596846</v>
+        <v>596612</v>
       </c>
       <c r="R15" t="n">
-        <v>6984733</v>
+        <v>6984853</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,6 +2027,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,10 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127104070</v>
+        <v>127104643</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596613</v>
+        <v>596858</v>
       </c>
       <c r="R16" t="n">
-        <v>6984838</v>
+        <v>6984703</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2302,113 +2162,6 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>127104643</v>
-      </c>
-      <c r="B17" t="n">
-        <v>57672</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Häbbersjöhöjden, Jmt</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>596858</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6984703</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Fors</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25016-2025 artfynd.xlsx
+++ b/artfynd/A 25016-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350823</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350827</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350822</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350824</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350828</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350831</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103710</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127104594</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350830</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350829</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350826</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103766</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1948,6 +2013,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127104070</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2055,6 +2125,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127104113</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2162,8 +2237,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127104643</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>